--- a/stories/arbres/TREE-COL-004.xlsx
+++ b/stories/arbres/TREE-COL-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est à l'école, avec maman. Papa viendra le soir. Sara écoute la maîtresse. Un camarade chuchote. Sara sent un malaise. Maman dit : on écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sara est à l'école, avec maman. Papa viendra le soir. Sara écoute la maîtresse. Un camarade chuchote. Sara sent un malaise. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est à l'école, avec maman. Papa viendra le soir. Sara écoute la maîtresse. Un camarade chuchote. Sara sent un malaise.
+maman|On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle du train. Sara a écouté la maîtresse. Un camarade chuchote. Sara a un malaise. Ce soir, raconter à la maison. Maman dit : je t'écoute.</t>
+          <t>À l'école, on parle du train. Sara a écouté la maîtresse. Un camarade chuchote. Sara a un malaise. Ce soir, raconter à la maison. Je t'écoute.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, on parle du train. Sara a écouté la maîtresse. Un camarade chuchote. Sara a un malaise. Ce soir, raconter à la maison.
+maman|Je t'écoute.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On écoute, et si malaise on raconte à la maison ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara respire. Maman est là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2229,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2398,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2593,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2760,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le train. Puis Tom. Puis le matin. On se tient la main. Sara tend le matin à papa. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2927,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3094,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Les chaussures font toc toc. Sara essuie ses mains. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3261,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3428,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de le train. Et de Tom. Et de le soir. On souffle doucement. Sara pose sa tête un moment. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3595,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3535,7 +3624,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman dit : je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3673,6 +3762,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste.
+maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3863,6 +3958,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4025,6 +4125,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le train. Sara s'arrête. Un ruban reste dans la poche. Sara caresse le doudou. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4292,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4459,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range Léa. après la sieste reste près de le train. Une cloche tinte, tout loin. Sara dit merci à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4626,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4535,7 +4655,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4673,6 +4793,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4960,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5127,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,6 +5322,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5349,6 +5489,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Sami est rangé. le train est fini. Un linge sèche à l'air. Sara serre la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5656,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5823,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sara pose Sami. le train est derrière. Le vent est doux. Sara raccroche un linge. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5990,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6157,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le soir. Maman a vu le train. Et Sami. Le sol est un peu froid. Sara chuchote : c'est fini. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6324,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6321,6 +6491,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, on parle du bus. Sara a écouté la maîtresse. Son ventre est serré. C'est un malaise. Si malaise, raconter à la maison. Sara le dira à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6672,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Un malaise : on raconte à la maison ?</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6845,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara retient le geste. Maman sourit. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7040,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6879,7 +7069,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman dit : je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7017,6 +7207,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin.
+maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7207,6 +7403,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7369,6 +7570,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le bus. Puis Tom. Puis le matin. On entend un oiseau. Sara boit une gorgée d'eau. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7737,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7904,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Un panier est posé sur le banc. Sara répète tout bas le geste. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8071,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8238,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de le bus. Et de Tom. Et de le soir. Une tasse cliquette. Sara sourit. Maman sourit aussi. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8405,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8572,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8531,6 +8767,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8693,6 +8934,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sara s'arrête. On attend son tour. Sara ferme le sac. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9101,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9268,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range Léa. après la sieste reste près de le bus. Ça sent le pain chaud. Sara s'assoit près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9435,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9203,7 +9464,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9341,6 +9602,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9769,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9936,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9855,6 +10131,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9879,7 +10160,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Sami est rangé. le bus est fini. On rit un peu. Sara dit : j'ai appris. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Sara rejoint le matin. Sami est rangé. le bus est fini. On rit un peu. J'ai appris. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10017,6 +10298,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Sami est rangé. le bus est fini. On rit un peu.
+enfant-f|J'ai appris. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison.
+narrateur|Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10467,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10634,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sara pose Sami. le bus est derrière. Une feuille tombe. Sara pose Sami à sa place. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10801,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10968,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le soir. Maman a vu le bus. Et Sami. L'eau coule, tout petit bruit. Sara enfile ses chaussons. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11135,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11164,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle de la voiture. Sara a écouté la maîtresse. Le malaise est là. Sara dit : ce soir je raconte. Si malaise, raconter à la maison.</t>
+          <t>À l'école, on parle de la voiture. Sara a écouté la maîtresse. Le malaise est là. Ce soir je raconte. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11302,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, on parle de la voiture. Sara a écouté la maîtresse. Le malaise est là.
+enfant-f|Ce soir je raconte. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11484,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On écoute la maîtresse ?</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara hoche la tête. On continue, avec maman. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11521,6 +11850,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11685,6 +12019,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11875,6 +12214,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12037,6 +12381,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la voiture. Puis Tom. Puis le matin. Un galet est encore chaud. Papa n'est pas loin. Sara les rejoint. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12548,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12715,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Sara range la voiture dans sa tête, comme un souvenir. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12882,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13049,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de la voiture. Et de Tom. Et de le soir. Un vélo passe au loin. Sara plie un pull. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13216,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13383,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13199,6 +13578,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13361,6 +13745,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sara s'arrête. La lumière est claire. Sara ferme la porte, tout doux. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13912,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14079,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range Léa. après la sieste reste près de la voiture. Un ballon s'immobilise. Sara range encore un peu, près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14246,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13871,7 +14275,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14009,6 +14413,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14580,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14195,7 +14609,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman dit : je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14333,6 +14747,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir.
+maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14523,6 +14943,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14685,6 +15110,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Sami est rangé. la voiture est fini. Il y a des miettes sur la table. Sara range la tasse. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15277,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15444,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sara pose Sami. la voiture est derrière. On range un objet. Sara prend la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15611,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15778,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le soir. Maman a vu la voiture. Et Sami. On dit merci. Sara souffle, puis sourit à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15945,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15544,6 +15999,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-004.xlsx
+++ b/stories/arbres/TREE-COL-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 maman|Je t'écoute.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|On écoute, et si malaise on raconte à la maison ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara respire. Maman est là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2236,6 +2246,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2403,6 +2414,7 @@
           <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2598,6 +2610,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2765,6 +2778,7 @@
           <t>narrateur|Sara a choisi le train. Puis Tom. Puis le matin. On se tient la main. Sara tend le matin à papa. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2932,6 +2946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3099,6 +3114,7 @@
           <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Les chaussures font toc toc. Sara essuie ses mains. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3266,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3433,6 +3450,7 @@
           <t>narrateur|Sara se souvient de le train. Et de Tom. Et de le soir. On souffle doucement. Sara pose sa tête un moment. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3600,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3768,6 +3787,7 @@
 maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3963,6 +3983,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4130,6 +4151,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le train. Sara s'arrête. Un ruban reste dans la poche. Sara caresse le doudou. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4297,6 +4319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4464,6 +4487,7 @@
           <t>narrateur|Sara range Léa. après la sieste reste près de le train. Une cloche tinte, tout loin. Sara dit merci à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4631,6 +4655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4798,6 +4823,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4965,6 +4991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5132,6 +5159,7 @@
           <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5327,6 +5355,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5494,6 +5523,7 @@
           <t>narrateur|Sara rejoint le matin. Sami est rangé. le train est fini. Un linge sèche à l'air. Sara serre la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5661,6 +5691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5828,6 +5859,7 @@
           <t>narrateur|Près de après la sieste. Sara pose Sami. le train est derrière. Le vent est doux. Sara raccroche un linge. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5995,6 +6027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6162,6 +6195,7 @@
           <t>narrateur|Sara montre le soir. Maman a vu le train. Et Sami. Le sol est un peu froid. Sara chuchote : c'est fini. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6329,6 +6363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6496,6 +6531,7 @@
           <t>narrateur|À l'école, on parle du bus. Sara a écouté la maîtresse. Son ventre est serré. C'est un malaise. Si malaise, raconter à la maison. Sara le dira à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6679,6 +6715,7 @@
           <t>narrateur|Un malaise : on raconte à la maison ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6850,6 +6887,7 @@
           <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara retient le geste. Maman sourit. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7045,6 +7083,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7213,6 +7252,7 @@
 maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7408,6 +7448,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7575,6 +7616,7 @@
           <t>narrateur|Sara a choisi le bus. Puis Tom. Puis le matin. On entend un oiseau. Sara boit une gorgée d'eau. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7742,6 +7784,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7909,6 +7952,7 @@
           <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Un panier est posé sur le banc. Sara répète tout bas le geste. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8076,6 +8120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8243,6 +8288,7 @@
           <t>narrateur|Sara se souvient de le bus. Et de Tom. Et de le soir. Une tasse cliquette. Sara sourit. Maman sourit aussi. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8410,6 +8456,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8577,6 +8624,7 @@
           <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8772,6 +8820,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8939,6 +8988,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sara s'arrête. On attend son tour. Sara ferme le sac. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9106,6 +9156,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9273,6 +9324,7 @@
           <t>narrateur|Sara range Léa. après la sieste reste près de le bus. Ça sent le pain chaud. Sara s'assoit près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9440,6 +9492,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9607,6 +9660,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9774,6 +9828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9941,6 +9996,7 @@
           <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10136,6 +10192,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10305,6 +10362,7 @@
 narrateur|Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10472,6 +10530,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10639,6 +10698,7 @@
           <t>narrateur|Près de après la sieste. Sara pose Sami. le bus est derrière. Une feuille tombe. Sara pose Sami à sa place. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10806,6 +10866,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10973,6 +11034,7 @@
           <t>narrateur|Sara montre le soir. Maman a vu le bus. Et Sami. L'eau coule, tout petit bruit. Sara enfile ses chaussons. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11140,6 +11202,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11308,6 +11371,7 @@
 enfant-f|Ce soir je raconte. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11491,6 +11555,7 @@
           <t>narrateur|On écoute la maîtresse ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11662,6 +11727,7 @@
           <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara hoche la tête. On continue, avec maman. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11857,6 +11923,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12024,6 +12091,7 @@
           <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12219,6 +12287,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12386,6 +12455,7 @@
           <t>narrateur|Sara a choisi la voiture. Puis Tom. Puis le matin. Un galet est encore chaud. Papa n'est pas loin. Sara les rejoint. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12553,6 +12623,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12720,6 +12791,7 @@
           <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Sara range la voiture dans sa tête, comme un souvenir. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12887,6 +12959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13054,6 +13127,7 @@
           <t>narrateur|Sara se souvient de la voiture. Et de Tom. Et de le soir. Un vélo passe au loin. Sara plie un pull. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13221,6 +13295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13388,6 +13463,7 @@
           <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13583,6 +13659,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13750,6 +13827,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sara s'arrête. La lumière est claire. Sara ferme la porte, tout doux. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13917,6 +13995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14084,6 +14163,7 @@
           <t>narrateur|Sara range Léa. après la sieste reste près de la voiture. Un ballon s'immobilise. Sara range encore un peu, près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14251,6 +14331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14418,6 +14499,7 @@
           <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14585,6 +14667,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14753,6 +14836,7 @@
 maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14948,6 +15032,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15115,6 +15200,7 @@
           <t>narrateur|Sara rejoint le matin. Sami est rangé. la voiture est fini. Il y a des miettes sur la table. Sara range la tasse. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15282,6 +15368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15449,6 +15536,7 @@
           <t>narrateur|Près de après la sieste. Sara pose Sami. la voiture est derrière. On range un objet. Sara prend la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15616,6 +15704,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15783,6 +15872,7 @@
           <t>narrateur|Sara montre le soir. Maman a vu la voiture. Et Sami. On dit merci. Sara souffle, puis sourit à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15950,6 +16040,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15968,7 +16059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16006,6 +16097,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16020,7 +16125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16207,6 +16312,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-004.xlsx
+++ b/stories/arbres/TREE-COL-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — à l'école</t>
+          <t>La cloche et le crayon jaune</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>À l'école, Sarah écoute la maîtresse. Un camarade chuchote. Son ventre se serre. À la maison, elle raconte à papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est à l'école, avec maman. Papa viendra le soir. Sara écoute la maîtresse. Un camarade chuchote. Sara sent un malaise. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>La cloche de l'école sonne une fois, toute ronde. Les carreaux du couloir sont froids sous les chaussures. Ça sent la craie et le savon des mains. Un rayon glisse sur le casier de Sarah. Le cartable est un peu lourd. Un crayon jaune dépasse, tout lisse. Maman s'arrête près de la porte de la classe. La poignée est froide. Bonne journée, Sarah. Tu écoutes la maîtresse, d'accord ? D'accord, maman. Papa t'écoute ce soir, à la maison. En ce moment, Sarah s'assoit. La chaise fait un petit toc. La maîtresse ouvre un grand livre. Il y a un train, un bus, une voiture. On écoute d'abord. Sarah écoute. Un camarade se penche. Il chuchote tout près de l'oreille. Sarah sent un malaise. Son ventre se serre, tout petit. Elle reste sur sa chaise. Elle écoute encore la maîtresse. À la maison, je raconte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,38 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara est à l'école, avec maman. Papa viendra le soir. Sara écoute la maîtresse. Un camarade chuchote. Sara sent un malaise.
-maman|On écoute la maîtresse. Si malaise, raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La cloche de l'école sonne une fois, toute ronde.
+narrateur|Les carreaux du couloir sont froids sous les chaussures.
+narrateur|Ça sent la craie et le savon des mains.
+narrateur|Un rayon glisse sur le casier de Sarah.
+narrateur|Le cartable est un peu lourd.
+narrateur|Un crayon jaune dépasse, tout lisse.
+narrateur|Maman s'arrête près de la porte de la classe.
+narrateur|La poignée est froide.
+maman|Bonne journée, Sarah.
+maman|Tu écoutes la maîtresse, d'accord ?
+enfant-f|D'accord, maman.
+maman|Papa t'écoute ce soir, à la maison.
+narrateur|En ce moment, Sarah s'assoit.
+narrateur|La chaise fait un petit toc.
+narrateur|La maîtresse ouvre un grand livre.
+narrateur|Il y a un train, un bus, une voiture.
+maitresse|On écoute d'abord.
+narrateur|Sarah écoute.
+narrateur|Un camarade se penche.
+narrateur|Il chuchote tout près de l'oreille.
+narrateur|Sarah sent un malaise.
+narrateur|Son ventre se serre, tout petit.
+narrateur|Elle reste sur sa chaise.
+narrateur|Elle écoute encore la maîtresse.
+enfant-f|À la maison, je raconte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cloche</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le train, le bus, ou la voiture.</t>
+          <t>Le livre a trois images. Le train, le bus, ou la voiture ? On écoute. Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1557,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+          <t>narrateur|Le livre a trois images.
+maitresse|Le train, le bus, ou la voiture ?
+maman|On écoute.
+maman|Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle du train. Sara a écouté la maîtresse. Un camarade chuchote. Sara a un malaise. Ce soir, raconter à la maison. Je t'écoute.</t>
+          <t>La maîtresse montre le train. Les roues sont noires, toutes rondes. Une petite cheminée est dessinée, tout gris. On écoute d'abord. Sarah écoute. Un camarade se penche. Il chuchote tout près. Sarah sent un malaise. Son ventre se serre, tout petit. Elle reste sur sa chaise. Elle écoute encore la maîtresse. Je raconte à la maison. Merci, Sarah. Tu as écouté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,8 +1728,20 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, on parle du train. Sara a écouté la maîtresse. Un camarade chuchote. Sara a un malaise. Ce soir, raconter à la maison.
-maman|Je t'écoute.</t>
+          <t>narrateur|La maîtresse montre le train.
+narrateur|Les roues sont noires, toutes rondes.
+narrateur|Une petite cheminée est dessinée, tout gris.
+maitresse|On écoute d'abord.
+narrateur|Sarah écoute.
+narrateur|Un camarade se penche.
+narrateur|Il chuchote tout près.
+narrateur|Sarah sent un malaise.
+narrateur|Son ventre se serre, tout petit.
+narrateur|Elle reste sur sa chaise.
+narrateur|Elle écoute encore la maîtresse.
+enfant-f|Je raconte à la maison.
+maitresse|Merci, Sarah.
+maitresse|Tu as écouté.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1715,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On écoute, et si malaise on raconte à la maison ?</t>
+          <t>Sarah a un malaise. Que fait-elle, à la maison ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1875,7 +1929,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On écoute, et si malaise on raconte à la maison ?</t>
+          <t>narrateur|Sarah a un malaise.
+maman|Que fait-elle, à la maison ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1903,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On écoute. Si malaise, raconter à la maison. Sara respire. Maman est là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, on raconte à la maison. Sarah respire. Je raconte à papa, ou à maman. On t'écoute. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2047,7 +2102,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara respire. Maman est là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+narrateur|Sarah respire.
+enfant-f|Je raconte à papa, ou à maman.
+papa|On t'écoute.
+papa|Bravo, Sarah.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2075,7 +2136,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le coin des peluches attend, près du casier. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2243,7 +2304,10 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le coin des peluches attend, près du casier.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2271,7 +2335,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Sarah l'assoit contre le casier. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Sarah caresse l'oreille de l'ours. On écoute la maîtresse. Si malaise, on raconte à la maison. L'ours a un ticket de train, collé au ventre. Sarah se souvient encore de le train. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2411,7 +2475,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Sarah l'assoit contre le casier.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Sarah caresse l'oreille de l'ours.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|L'ours a un ticket de train, collé au ventre.
+narrateur|Sarah se souvient encore de le train.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2439,7 +2517,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2607,7 +2685,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2635,7 +2715,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le train. Puis Tom. Puis le matin. On se tient la main. Sara tend le matin à papa. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. L'ours Tom est sur la chaise, près du cacao. Sarah se souvient de le train. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2775,7 +2855,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le train. Puis Tom. Puis le matin. On se tient la main. Sara tend le matin à papa. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|L'ours Tom est sur la chaise, près du cacao.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2803,7 +2904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu l'ours Tom. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2943,7 +3044,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu l'ours Tom. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2971,7 +3078,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sara s'arrête près de après la sieste. Tom est rangé. Les chaussures font toc toc. Sara essuie ses mains. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. L'ours Tom a glissé sous la couverture. Sarah se souvient de le train. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3111,7 +3218,29 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Les chaussures font toc toc. Sara essuie ses mains. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|L'ours Tom a glissé sous la couverture.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3139,7 +3268,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu l'ours Tom. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3279,7 +3408,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu l'ours Tom. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3307,7 +3442,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara se souvient de le train. Et de Tom. Et de le soir. On souffle doucement. Sara pose sa tête un moment. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. L'ours Tom est près de l'assiette, tout sage. Sarah se souvient de le train. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3447,7 +3582,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sara se souvient de le train. Et de Tom. Et de le soir. On souffle doucement. Sara pose sa tête un moment. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|L'ours Tom est près de l'assiette, tout sage.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3475,7 +3631,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu l'ours Tom. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3615,7 +3771,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu l'ours Tom. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3643,7 +3805,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Sarah pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Sarah lisse la robe bleue. Le malaise est encore là, tout petit. La poupée a un chapeau, comme le contrôleur. Sarah se souvient encore de le train. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3783,8 +3945,21 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste.
-maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Sarah pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Sarah lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée a un chapeau, comme le contrôleur.
+narrateur|Sarah se souvient encore de le train.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3812,7 +3987,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3980,7 +4155,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4008,7 +4185,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le train. Sara s'arrête. Un ruban reste dans la poche. Sara caresse le doudou. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. La poupée Léa a un peu de cacao sur la robe. Sarah se souvient de le train. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4148,7 +4325,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le train. Sara s'arrête. Un ruban reste dans la poche. Sara caresse le doudou. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|La poupée Léa a un peu de cacao sur la robe.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4176,7 +4374,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu la poupée Léa. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4316,7 +4514,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu la poupée Léa. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4344,7 +4548,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sara range Léa. après la sieste reste près de le train. Une cloche tinte, tout loin. Sara dit merci à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. La poupée Léa veille au bord du lit. Sarah se souvient de le train. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4484,7 +4688,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sara range Léa. après la sieste reste près de le train. Une cloche tinte, tout loin. Sara dit merci à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|La poupée Léa veille au bord du lit.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4512,7 +4738,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu la poupée Léa. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4652,7 +4878,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu la poupée Léa. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4680,7 +4912,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. La poupée Léa est sur la nappe, loin de la soupe. Sarah se souvient de le train. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4820,7 +5052,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une chaussette est encore sablée. Sara marche près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|La poupée Léa est sur la nappe, loin de la soupe.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4848,7 +5101,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu la poupée Léa. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4988,7 +5241,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu la poupée Léa. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5016,7 +5275,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sarah tient Sami contre son cartable. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Sarah range une mèche de laine. Le crayon jaune est encore dans la poche. Le lion a une petite valise, tout carton. Sarah se souvient encore de le train. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5156,7 +5415,20 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Tom. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Sarah tient Sami contre son cartable.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+narrateur|Sarah range une mèche de laine.
+narrateur|Le crayon jaune est encore dans la poche.
+narrateur|Le lion a une petite valise, tout carton.
+narrateur|Sarah se souvient encore de le train.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5184,7 +5456,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5352,7 +5624,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5380,7 +5654,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Sami est rangé. le train est fini. Un linge sèche à l'air. Sara serre la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. Le lion Sami a une miette dans la crinière. Sarah se souvient de le train. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5520,7 +5794,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Sami est rangé. le train est fini. Un linge sèche à l'air. Sara serre la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|Le lion Sami a une miette dans la crinière.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5548,7 +5843,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu le lion Sami. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5688,7 +5983,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu le lion Sami. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5716,7 +6017,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sara pose Sami. le train est derrière. Le vent est doux. Sara raccroche un linge. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. Le lion Sami chauffe au soleil du volet. Sarah se souvient de le train. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5856,7 +6157,29 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sara pose Sami. le train est derrière. Le vent est doux. Sara raccroche un linge. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|Le lion Sami chauffe au soleil du volet.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5884,7 +6207,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu le lion Sami. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6024,7 +6347,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu le lion Sami. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6052,7 +6381,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sara montre le soir. Maman a vu le train. Et Sami. Le sol est un peu froid. Sara chuchote : c'est fini. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. Le lion Sami écoute la cuillère, tout calme. Sarah se souvient de le train. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6192,7 +6521,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sara montre le soir. Maman a vu le train. Et Sami. Le sol est un peu froid. Sara chuchote : c'est fini. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|Le lion Sami écoute la cuillère, tout calme.
+narrateur|Sarah se souvient de le train.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6220,7 +6570,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le train. Elle a tenu le lion Sami. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6360,7 +6710,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le train. Elle a tenu le lion Sami. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6388,7 +6744,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle du bus. Sara a écouté la maîtresse. Son ventre est serré. C'est un malaise. Si malaise, raconter à la maison. Sara le dira à papa ou maman.</t>
+          <t>La maîtresse montre le bus. Les fenêtres sont jaunes, toutes alignées. Un petit volant est dessiné, tout rond. On écoute le bus, ensemble. Sarah écoute. Un camarade chuchote derrière le livre. Sarah a un malaise. Ses mains deviennent chaudes. Elle pose le crayon, tout droit. Elle écoute la maîtresse jusqu'au bout. Maman m'écoute, à la maison. Oui. D'abord on écoute ici.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6528,7 +6884,19 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, on parle du bus. Sara a écouté la maîtresse. Son ventre est serré. C'est un malaise. Si malaise, raconter à la maison. Sara le dira à papa ou maman.</t>
+          <t>narrateur|La maîtresse montre le bus.
+narrateur|Les fenêtres sont jaunes, toutes alignées.
+narrateur|Un petit volant est dessiné, tout rond.
+maitresse|On écoute le bus, ensemble.
+narrateur|Sarah écoute.
+narrateur|Un camarade chuchote derrière le livre.
+narrateur|Sarah a un malaise.
+narrateur|Ses mains deviennent chaudes.
+narrateur|Elle pose le crayon, tout droit.
+narrateur|Elle écoute la maîtresse jusqu'au bout.
+enfant-f|Maman m'écoute, à la maison.
+maitresse|Oui.
+maitresse|D'abord on écoute ici.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6556,7 +6924,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Un malaise : on raconte à la maison ?</t>
+          <t>On écoute la maîtresse. Et si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6712,7 +7080,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Un malaise : on raconte à la maison ?</t>
+          <t>narrateur|On écoute la maîtresse.
+papa|Et si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6740,7 +7109,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On écoute. Si malaise, raconter à la maison. Sara retient le geste. Maman sourit. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Oui. On écoute. Si malaise, raconter à la maison. Sarah essuie ses mains sur sa robe. J'ai écouté. Et tu nous racontes. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6884,7 +7253,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara retient le geste. Maman sourit. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>papa|Oui.
+papa|On écoute.
+papa|Si malaise, raconter à la maison.
+narrateur|Sarah essuie ses mains sur sa robe.
+enfant-f|J'ai écouté.
+maman|Et tu nous racontes.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6912,7 +7287,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le coin des peluches attend, près du casier. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7080,7 +7455,10 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le coin des peluches attend, près du casier.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7108,7 +7486,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Sarah l'assoit contre le casier. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Sarah caresse l'oreille de l'ours. On écoute la maîtresse. Si malaise, on raconte à la maison. L'ours est assis comme dans un bus, tout droit. Sarah se souvient encore de le bus. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7248,8 +7626,21 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin.
-maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Sarah l'assoit contre le casier.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Sarah caresse l'oreille de l'ours.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|L'ours est assis comme dans un bus, tout droit.
+narrateur|Sarah se souvient encore de le bus.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7277,7 +7668,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7445,7 +7836,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7473,7 +7866,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le bus. Puis Tom. Puis le matin. On entend un oiseau. Sara boit une gorgée d'eau. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. L'ours Tom est dans le cartable, près de la porte. Sarah se souvient de le bus. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7613,7 +8006,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le bus. Puis Tom. Puis le matin. On entend un oiseau. Sara boit une gorgée d'eau. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|L'ours Tom est dans le cartable, près de la porte.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7641,7 +8055,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu l'ours Tom. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7781,7 +8195,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu l'ours Tom. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7809,7 +8229,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara s'arrête près de après la sieste. Tom est rangé. Un panier est posé sur le banc. Sara répète tout bas le geste. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. L'ours Tom a l'oreille pliée, comme un ticket. Sarah se souvient de le bus. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7949,7 +8369,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Un panier est posé sur le banc. Sara répète tout bas le geste. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|L'ours Tom a l'oreille pliée, comme un ticket.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7977,7 +8419,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu l'ours Tom. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8117,7 +8559,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu l'ours Tom. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8145,7 +8593,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sara se souvient de le bus. Et de Tom. Et de le soir. Une tasse cliquette. Sara sourit. Maman sourit aussi. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. L'ours Tom sent encore le savon de l'école. Sarah se souvient de le bus. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8285,7 +8733,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sara se souvient de le bus. Et de Tom. Et de le soir. Une tasse cliquette. Sara sourit. Maman sourit aussi. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|L'ours Tom sent encore le savon de l'école.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8313,7 +8782,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu l'ours Tom. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8453,7 +8922,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu l'ours Tom. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8481,7 +8956,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Sarah pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Sarah lisse la robe bleue. Le malaise est encore là, tout petit. La poupée a un ticket jaune, tout plié. Sarah se souvient encore de le bus. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8621,7 +9096,21 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Sarah pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Sarah lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée a un ticket jaune, tout plié.
+narrateur|Sarah se souvient encore de le bus.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8649,7 +9138,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8817,7 +9306,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8845,7 +9336,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le bus. Sara s'arrête. On attend son tour. Sara ferme le sac. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. La poupée Léa est près du bol, tout droite. Sarah se souvient de le bus. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8985,7 +9476,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sara s'arrête. On attend son tour. Sara ferme le sac. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|La poupée Léa est près du bol, tout droite.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9013,7 +9525,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu la poupée Léa. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9153,7 +9665,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu la poupée Léa. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9181,7 +9699,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sara range Léa. après la sieste reste près de le bus. Ça sent le pain chaud. Sara s'assoit près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. La poupée Léa a la robe froissée, après la sieste. Sarah se souvient de le bus. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9321,7 +9839,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sara range Léa. après la sieste reste près de le bus. Ça sent le pain chaud. Sara s'assoit près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|La poupée Léa a la robe froissée, après la sieste.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9349,7 +9889,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu la poupée Léa. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9489,7 +10029,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu la poupée Léa. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9517,7 +10063,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. La poupée Léa a un ticket jaune dans la poche. Sarah se souvient de le bus. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9657,7 +10203,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. La couverture est douce. Sara montre le soir à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|La poupée Léa a un ticket jaune dans la poche.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9685,7 +10252,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu la poupée Léa. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9825,7 +10392,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu la poupée Léa. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9853,7 +10426,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sarah tient Sami contre son cartable. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Sarah range une mèche de laine. Le crayon jaune est encore dans la poche. Le lion regarde la fenêtre du livre, tout loin. Sarah se souvient encore de le bus. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9993,7 +10566,20 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Léa. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Sarah tient Sami contre son cartable.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+narrateur|Sarah range une mèche de laine.
+narrateur|Le crayon jaune est encore dans la poche.
+narrateur|Le lion regarde la fenêtre du livre, tout loin.
+narrateur|Sarah se souvient encore de le bus.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10021,7 +10607,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10189,7 +10775,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10217,7 +10805,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Sami est rangé. le bus est fini. On rit un peu. J'ai appris. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. Le lion Sami baille, tout doux, près du cacao. Sarah se souvient de le bus. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10357,9 +10945,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Sami est rangé. le bus est fini. On rit un peu.
-enfant-f|J'ai appris. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison.
-narrateur|Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|Le lion Sami baille, tout doux, près du cacao.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10387,7 +10994,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu le lion Sami. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10527,7 +11134,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu le lion Sami. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10555,7 +11168,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sara pose Sami. le bus est derrière. Une feuille tombe. Sara pose Sami à sa place. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. Le lion Sami a chaud, sous la couverture. Sarah se souvient de le bus. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10695,7 +11308,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sara pose Sami. le bus est derrière. Une feuille tombe. Sara pose Sami à sa place. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|Le lion Sami a chaud, sous la couverture.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10723,7 +11358,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu le lion Sami. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10863,7 +11498,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu le lion Sami. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10891,7 +11532,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara montre le soir. Maman a vu le bus. Et Sami. L'eau coule, tout petit bruit. Sara enfile ses chaussons. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. Le lion Sami a une goutte de soupe sur la laine. Sarah se souvient de le bus. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11031,7 +11672,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sara montre le soir. Maman a vu le bus. Et Sami. L'eau coule, tout petit bruit. Sara enfile ses chaussons. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|Le lion Sami a une goutte de soupe sur la laine.
+narrateur|Sarah se souvient de le bus.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11059,7 +11721,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu le bus. Elle a tenu le lion Sami. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11199,7 +11861,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu le bus. Elle a tenu le lion Sami. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11227,7 +11895,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>À l'école, on parle de la voiture. Sara a écouté la maîtresse. Le malaise est là. Ce soir je raconte. Si malaise, raconter à la maison.</t>
+          <t>La maîtresse montre la voiture. Les phares sont blancs, tout petits. Une porte est ouverte, sur le papier. On écoute. Sarah écoute. Le malaise est là, dans le ventre. Un camarade a parlé tout bas. Sarah respire. Ce soir, je raconte. Tu as bien écouté le livre. Sarah garde le crayon jaune dans la main. Le bois est lisse.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11367,8 +12035,18 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|À l'école, on parle de la voiture. Sara a écouté la maîtresse. Le malaise est là.
-enfant-f|Ce soir je raconte. Si malaise, raconter à la maison.</t>
+          <t>narrateur|La maîtresse montre la voiture.
+narrateur|Les phares sont blancs, tout petits.
+narrateur|Une porte est ouverte, sur le papier.
+maitresse|On écoute.
+narrateur|Sarah écoute.
+narrateur|Le malaise est là, dans le ventre.
+narrateur|Un camarade a parlé tout bas.
+narrateur|Sarah respire.
+enfant-f|Ce soir, je raconte.
+maitresse|Tu as bien écouté le livre.
+narrateur|Sarah garde le crayon jaune dans la main.
+narrateur|Le bois est lisse.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11396,7 +12074,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On écoute la maîtresse ?</t>
+          <t>À l'école, Sarah a écouté. On écoute la maîtresse ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11552,7 +12230,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On écoute la maîtresse ?</t>
+          <t>narrateur|À l'école, Sarah a écouté.
+maman|On écoute la maîtresse ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11580,7 +12259,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On écoute. Si malaise, raconter à la maison. Sara hoche la tête. On continue, avec maman. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à papa ou maman. Sarah hoche la tête. J'écoute. Puis je raconte. Bravo. On continue ensemble.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11724,7 +12403,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On écoute. Si malaise, raconter à la maison. Sara hoche la tête. On continue, avec maman. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à papa ou maman.
+narrateur|Sarah hoche la tête.
+enfant-f|J'écoute.
+enfant-f|Puis je raconte.
+papa|Bravo.
+papa|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11752,7 +12438,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Le coin des peluches attend, près du casier. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11920,7 +12606,10 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Le coin des peluches attend, près du casier.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11948,7 +12637,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Sarah l'assoit contre le casier. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Sarah caresse l'oreille de l'ours. On écoute la maîtresse. Si malaise, on raconte à la maison. L'ours a une ceinture de papier, tout simple. Sarah se souvient encore de la voiture. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12088,7 +12777,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le matin. Maman reste tout près. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Sarah l'assoit contre le casier.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+narrateur|Sarah caresse l'oreille de l'ours.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|L'ours a une ceinture de papier, tout simple.
+narrateur|Sarah se souvient encore de la voiture.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12116,7 +12819,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12284,7 +12987,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12312,7 +13017,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi la voiture. Puis Tom. Puis le matin. Un galet est encore chaud. Papa n'est pas loin. Sara les rejoint. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. L'ours Tom a la ceinture de papier, encore là. Sarah se souvient de la voiture. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12452,7 +13157,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi la voiture. Puis Tom. Puis le matin. Un galet est encore chaud. Papa n'est pas loin. Sara les rejoint. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|L'ours Tom a la ceinture de papier, encore là.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12480,7 +13206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu l'ours Tom. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12620,7 +13346,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu l'ours Tom. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12648,7 +13380,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sara s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Sara range la voiture dans sa tête, comme un souvenir. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. L'ours Tom ronronne presque, tout brun. Sarah se souvient de la voiture. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12788,7 +13520,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sara s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Sara range la voiture dans sa tête, comme un souvenir. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|L'ours Tom ronronne presque, tout brun.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12816,7 +13570,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu l'ours Tom. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12956,7 +13710,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu l'ours Tom. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12984,7 +13744,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sara se souvient de la voiture. Et de Tom. Et de le soir. Un vélo passe au loin. Sara plie un pull. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. L'ours Tom regarde la fenêtre de la cuisine. Sarah se souvient de la voiture. Elle tient encore l'ours Tom. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13124,7 +13884,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sara se souvient de la voiture. Et de Tom. Et de le soir. Un vélo passe au loin. Sara plie un pull. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|L'ours Tom regarde la fenêtre de la cuisine.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore l'ours Tom.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13152,7 +13933,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu l'ours Tom. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13292,7 +14073,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu l'ours Tom. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13320,7 +14107,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Sarah pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Sarah lisse la robe bleue. Le malaise est encore là, tout petit. La poupée tient un volant de carton. Sarah se souvient encore de la voiture. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13460,7 +14247,21 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est après la sieste. Maman montre le geste, lentement. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Sarah pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Sarah lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée tient un volant de carton.
+narrateur|Sarah se souvient encore de la voiture.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13488,7 +14289,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13656,7 +14457,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13684,7 +14487,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de la voiture. Sara s'arrête. La lumière est claire. Sara ferme la porte, tout doux. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. La poupée Léa tient encore le volant de carton. Sarah se souvient de la voiture. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13824,7 +14627,28 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sara s'arrête. La lumière est claire. Sara ferme la porte, tout doux. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|La poupée Léa tient encore le volant de carton.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13852,7 +14676,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu la poupée Léa. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13992,7 +14816,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu la poupée Léa. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14020,7 +14850,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sara range Léa. après la sieste reste près de la voiture. Un ballon s'immobilise. Sara range encore un peu, près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. La poupée Léa a un bouton défait, tout petit. Sarah se souvient de la voiture. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14160,7 +14990,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sara range Léa. après la sieste reste près de la voiture. Un ballon s'immobilise. Sara range encore un peu, près de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|La poupée Léa a un bouton défait, tout petit.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14188,7 +15040,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu la poupée Léa. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14328,7 +15180,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu la poupée Léa. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14356,7 +15214,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. La poupée Léa est sur les genoux, près de la lampe. Sarah se souvient de la voiture. Elle tient encore la poupée Léa. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14496,7 +15354,28 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. Un chat miaule une fois. Sara écoute maman encore une fois. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|La poupée Léa est sur les genoux, près de la lampe.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore la poupée Léa.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14524,7 +15403,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu la poupée Léa. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14664,7 +15543,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu la poupée Léa. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14692,7 +15577,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir. Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>Sarah rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Sarah tient Sami contre son cartable. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Sarah range une mèche de laine. Le crayon jaune est encore dans la poche. Le lion a une clé de bois, trop grande. Sarah se souvient encore de la voiture. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14832,8 +15717,20 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sara parle à Sami. Elle a écouté la maîtresse. Elle a un malaise. Si malaise, raconter à la maison. C'est le soir.
-maman|Je suis là. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Sarah rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Sarah tient Sami contre son cartable.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+narrateur|Sarah range une mèche de laine.
+narrateur|Le crayon jaune est encore dans la poche.
+narrateur|Le lion a une clé de bois, trop grande.
+narrateur|Sarah se souvient encore de la voiture.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14861,7 +15758,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Sarah racontera, à la maison. Le matin, après la sieste, ou le soir ? On t'écoute.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15029,7 +15926,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Sarah racontera, à la maison.
+maman|Le matin, après la sieste, ou le soir ?
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15057,7 +15956,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin. Sami est rangé. la voiture est fini. Il y a des miettes sur la table. Sara range la tasse. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le matin, la cuisine sent le cacao. La tasse est chaude, tout près des mains. Une miette reste sur la table. Bonjour, Sarah. Tu as dormi ? Un peu. Le lion Sami a la clé de bois, trop grande. Sarah se souvient de la voiture. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15197,7 +16096,28 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint le matin. Sami est rangé. la voiture est fini. Il y a des miettes sur la table. Sara range la tasse. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le matin, la cuisine sent le cacao.
+narrateur|La tasse est chaude, tout près des mains.
+narrateur|Une miette reste sur la table.
+papa|Bonjour, Sarah.
+maman|Tu as dormi ?
+enfant-f|Un peu.
+narrateur|Le lion Sami a la clé de bois, trop grande.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15225,7 +16145,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu le lion Sami. Le matin, elle a parlé. La tasse de cacao est presque vide. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15365,7 +16285,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu le lion Sami. Le matin, elle a parlé.
+narrateur|La tasse de cacao est presque vide.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15393,7 +16319,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sara pose Sami. la voiture est derrière. On range un objet. Sara prend la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Après la sieste, la couverture est tiède. Une joue de Sarah est encore marquée. Le volet fait une raie de lumière. Tu es réveillée ? Oui, maman. Viens. On a le temps. Le lion Sami a la crinière plate, après la sieste. Sarah se souvient de la voiture. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15533,7 +16459,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sara pose Sami. la voiture est derrière. On range un objet. Sara prend la main de maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Après la sieste, la couverture est tiède.
+narrateur|Une joue de Sarah est encore marquée.
+narrateur|Le volet fait une raie de lumière.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+papa|Viens.
+papa|On a le temps.
+narrateur|Le lion Sami a la crinière plate, après la sieste.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15561,7 +16509,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu le lion Sami. Après la sieste, elle a parlé. La couverture retombe, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15701,7 +16649,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu le lion Sami. Après la sieste, elle a parlé.
+narrateur|La couverture retombe, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15729,7 +16683,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sara montre le soir. Maman a vu la voiture. Et Sami. On dit merci. Sara souffle, puis sourit à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>Le soir, la soupe fume dans les assiettes. La lampe fait un rond jaune sur la nappe. Ça sent le pain. Te voilà. Assieds-toi, Sarah. J'ai quelque chose. Le lion Sami écoute la soupe, tout près. Sarah se souvient de la voiture. Elle tient encore le lion Sami. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Sarah. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15869,7 +16823,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sara montre le soir. Maman a vu la voiture. Et Sami. On dit merci. Sara souffle, puis sourit à maman. On écoute la maîtresse. Si malaise, raconter à la maison. On écoute. Si malaise, on raconte à papa ou maman, à la maison. Sara dit merci à maman.</t>
+          <t>narrateur|Le soir, la soupe fume dans les assiettes.
+narrateur|La lampe fait un rond jaune sur la nappe.
+narrateur|Ça sent le pain.
+papa|Te voilà.
+maman|Assieds-toi, Sarah.
+enfant-f|J'ai quelque chose.
+narrateur|Le lion Sami écoute la soupe, tout près.
+narrateur|Sarah se souvient de la voiture.
+narrateur|Elle tient encore le lion Sami.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Sarah se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15897,7 +16872,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Sarah. Tu as fait du bon travail. Sarah a vu la voiture. Elle a tenu le lion Sami. Le soir, elle a parlé. La lampe reste allumée, un moment. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16037,7 +17012,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Sarah a vu la voiture. Elle a tenu le lion Sami. Le soir, elle a parlé.
+narrateur|La lampe reste allumée, un moment.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16059,7 +17040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16111,6 +17092,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
